--- a/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
+++ b/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B5734D-8B42-40BB-8796-A25DC3140BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E1687A-8DF9-4B08-B6DB-70D7E36B3679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="247">
   <si>
     <t>Scenario</t>
   </si>
@@ -4740,12 +4740,79 @@
       <t>Poenari Castle</t>
     </r>
   </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Castle - Imperial Age</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Technologies</t>
+  </si>
+  <si>
+    <t>Unrestricted</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>Imperial Age</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer
+Hussar
+Heavy Camel Rider</t>
+  </si>
+  <si>
+    <t>No Dock
+No Barracks
+No Archery Range
+No Stable
+No Siege Workshop
+No Castle
+No Wonder</t>
+  </si>
+  <si>
+    <t>Magyars recieve Melee Attack Upgrades automatically</t>
+  </si>
+  <si>
+    <t>Turks recieve Chemistry and Hussar automatically</t>
+  </si>
+  <si>
+    <t>No Wonder</t>
+  </si>
+  <si>
+    <t>Slavs recieve Gambersons automatically</t>
+  </si>
+  <si>
+    <t>No Wonder
+No Dock
+No Fish Traps</t>
+  </si>
+  <si>
+    <t>No Naval Units
+No Trebuchets
+No Rams
+No Petards</t>
+  </si>
+  <si>
+    <t>No Capped Ram
+No Siege Ram
+No Spies
+Slavs recieve Gambersons automatically</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4885,6 +4952,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4894,7 +4974,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -5004,11 +5084,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5098,6 +5202,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5746,15 +5880,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F02C8E1-0617-48AE-97CC-71F03F7EACB1}">
-  <dimension ref="G1:L52"/>
+  <dimension ref="B1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -5768,7 +5908,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
       <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
@@ -5782,7 +5927,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>118</v>
       </c>
@@ -5796,7 +5950,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>241</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>119</v>
       </c>
@@ -5810,7 +5973,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
       <c r="G6" s="13" t="s">
         <v>108</v>
       </c>
@@ -5824,7 +5990,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
       <c r="G7" s="13" t="s">
         <v>90</v>
       </c>
@@ -5838,7 +6007,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="39"/>
       <c r="G8" s="13" t="s">
         <v>92</v>
       </c>
@@ -5852,7 +6024,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
       <c r="G9" s="13" t="s">
         <v>93</v>
       </c>
@@ -5866,7 +6041,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
       <c r="G10" s="13" t="s">
         <v>83</v>
       </c>
@@ -5880,7 +6058,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="39"/>
       <c r="G11" s="13" t="s">
         <v>120</v>
       </c>
@@ -5894,7 +6075,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
       <c r="G12" s="13" t="s">
         <v>97</v>
       </c>
@@ -5908,7 +6092,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="13" t="s">
         <v>121</v>
       </c>
@@ -5922,7 +6109,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
       <c r="G14" s="13" t="s">
         <v>133</v>
       </c>
@@ -5936,7 +6126,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
       <c r="G15" s="13" t="s">
         <v>132</v>
       </c>
@@ -5950,7 +6143,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
       <c r="G16" s="16" t="s">
         <v>131</v>
       </c>
@@ -6241,21 +6437,31 @@
       <c r="L52" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D5B1F3-605B-4EBE-ADC3-86093F9414AB}">
-  <dimension ref="G1:L52"/>
+  <dimension ref="B1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -6269,7 +6475,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>123</v>
       </c>
@@ -6283,7 +6494,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="G4" s="16" t="s">
         <v>142</v>
       </c>
@@ -6297,7 +6517,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="B5" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>240</v>
+      </c>
       <c r="G5" s="16" t="s">
         <v>95</v>
       </c>
@@ -6311,7 +6540,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
       <c r="G6" s="16" t="s">
         <v>112</v>
       </c>
@@ -6325,7 +6557,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
       <c r="G7" s="16" t="s">
         <v>143</v>
       </c>
@@ -6339,7 +6574,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="39"/>
       <c r="G8" s="16" t="s">
         <v>144</v>
       </c>
@@ -6353,7 +6591,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
       <c r="G9" s="16" t="s">
         <v>108</v>
       </c>
@@ -6367,7 +6608,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
       <c r="G10" s="16" t="s">
         <v>90</v>
       </c>
@@ -6381,7 +6625,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="39"/>
       <c r="G11" s="16" t="s">
         <v>145</v>
       </c>
@@ -6395,7 +6642,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
       <c r="G12" s="16" t="s">
         <v>146</v>
       </c>
@@ -6409,7 +6659,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="16" t="s">
         <v>106</v>
       </c>
@@ -6423,7 +6676,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
       <c r="G14" s="16" t="s">
         <v>97</v>
       </c>
@@ -6437,7 +6693,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
       <c r="G15" s="16" t="s">
         <v>113</v>
       </c>
@@ -6451,7 +6710,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
       <c r="G16" s="16" t="s">
         <v>148</v>
       </c>
@@ -6842,21 +7104,31 @@
       <c r="L52" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E160A0EB-2282-4E17-8E90-A75C2FBB2FDB}">
-  <dimension ref="G1:L52"/>
+  <dimension ref="B1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -6870,7 +7142,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
       <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
@@ -6884,7 +7161,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>173</v>
       </c>
@@ -6898,7 +7184,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>243</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>174</v>
       </c>
@@ -6912,7 +7207,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
       <c r="G6" s="26" t="s">
         <v>97</v>
       </c>
@@ -6926,7 +7224,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
       <c r="G7" s="26" t="s">
         <v>175</v>
       </c>
@@ -6940,7 +7241,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="39"/>
       <c r="G8" s="17" t="s">
         <v>176</v>
       </c>
@@ -6954,7 +7258,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
       <c r="G9" s="17" t="s">
         <v>177</v>
       </c>
@@ -6968,7 +7275,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
       <c r="G10" s="17" t="s">
         <v>178</v>
       </c>
@@ -6982,7 +7292,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="39"/>
       <c r="G11" s="17" t="s">
         <v>182</v>
       </c>
@@ -6996,7 +7309,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
       <c r="G12" s="17" t="s">
         <v>179</v>
       </c>
@@ -7010,7 +7326,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="17" t="s">
         <v>180</v>
       </c>
@@ -7024,7 +7343,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
       <c r="G14" s="17" t="s">
         <v>181</v>
       </c>
@@ -7038,7 +7360,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
       <c r="G15" s="17" t="s">
         <v>106</v>
       </c>
@@ -7052,7 +7377,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
       <c r="G16" s="14" t="s">
         <v>95</v>
       </c>
@@ -7463,21 +7791,31 @@
       <c r="L52" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D5F9A79-9995-4745-9487-825DE3743A9E}">
-  <dimension ref="G1:L52"/>
+  <dimension ref="B1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -7491,7 +7829,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
       <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
@@ -7505,7 +7848,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="G4" s="9" t="s">
         <v>118</v>
       </c>
@@ -7519,7 +7871,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>246</v>
+      </c>
       <c r="G5" s="9" t="s">
         <v>173</v>
       </c>
@@ -7533,7 +7894,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
       <c r="G6" s="14" t="s">
         <v>204</v>
       </c>
@@ -7547,7 +7911,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
       <c r="G7" s="14" t="s">
         <v>106</v>
       </c>
@@ -7561,7 +7928,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="39"/>
       <c r="G8" s="14" t="s">
         <v>90</v>
       </c>
@@ -7575,7 +7945,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
       <c r="G9" s="14" t="s">
         <v>121</v>
       </c>
@@ -7589,7 +7962,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
       <c r="G10" s="16" t="s">
         <v>104</v>
       </c>
@@ -7603,7 +7979,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="39"/>
       <c r="G11" s="16" t="s">
         <v>159</v>
       </c>
@@ -7617,7 +7996,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
       <c r="G12" s="16" t="s">
         <v>150</v>
       </c>
@@ -7631,7 +8013,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="16" t="s">
         <v>148</v>
       </c>
@@ -7645,7 +8030,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
       <c r="G14" s="16" t="s">
         <v>153</v>
       </c>
@@ -7659,7 +8047,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
       <c r="G15" s="13" t="s">
         <v>108</v>
       </c>
@@ -7673,7 +8064,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
       <c r="G16" s="13" t="s">
         <v>175</v>
       </c>
@@ -7984,21 +8378,31 @@
       <c r="L52" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39F4FDB-FAC5-4FF4-809E-E36473FC3DC6}">
-  <dimension ref="G1:L52"/>
+  <dimension ref="B1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="4" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -8012,7 +8416,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
       <c r="G3" s="21" t="s">
         <v>97</v>
       </c>
@@ -8026,7 +8435,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="G4" s="13" t="s">
         <v>123</v>
       </c>
@@ -8040,7 +8458,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>240</v>
+      </c>
       <c r="G5" s="13" t="s">
         <v>108</v>
       </c>
@@ -8054,7 +8481,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
       <c r="G6" s="13" t="s">
         <v>142</v>
       </c>
@@ -8068,7 +8498,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
       <c r="G7" s="13" t="s">
         <v>175</v>
       </c>
@@ -8082,7 +8515,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="39"/>
       <c r="G8" s="13" t="s">
         <v>215</v>
       </c>
@@ -8096,7 +8532,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
       <c r="G9" s="13" t="s">
         <v>90</v>
       </c>
@@ -8110,7 +8549,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
       <c r="G10" s="13" t="s">
         <v>104</v>
       </c>
@@ -8124,7 +8566,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="39"/>
       <c r="G11" s="13" t="s">
         <v>93</v>
       </c>
@@ -8138,7 +8583,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
       <c r="G12" s="9" t="s">
         <v>216</v>
       </c>
@@ -8152,7 +8600,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="26" t="s">
         <v>92</v>
       </c>
@@ -8166,7 +8617,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
       <c r="G14" s="26" t="s">
         <v>143</v>
       </c>
@@ -8180,7 +8634,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
       <c r="G15" s="26" t="s">
         <v>101</v>
       </c>
@@ -8194,7 +8651,10 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
       <c r="G16" s="26" t="s">
         <v>113</v>
       </c>
@@ -8581,6 +9041,10 @@
       <c r="L52" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
+++ b/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E1687A-8DF9-4B08-B6DB-70D7E36B3679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A43582F-2A6F-4059-BEC6-043127A63A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Vlad Dracula" sheetId="1" r:id="rId1"/>
@@ -4802,17 +4802,57 @@
 No Petards</t>
   </si>
   <si>
-    <t>No Capped Ram
+    <r>
+      <t xml:space="preserve">No Capped Ram
 No Siege Ram
 No Spies
-Slavs recieve Gambersons automatically</t>
+Slavs recieve Gambersons automatically
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Moderate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+Halberdier, Two-Handed Swordsman, Cavalier, Hussar, Conscription, Onager and Blast Furnace are researched automatically
+On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Standard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+All Military Technologies are researched automatically</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4962,6 +5002,12 @@
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -5204,6 +5250,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5220,18 +5278,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5890,11 +5936,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -5909,11 +5955,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
@@ -5951,13 +5997,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="31" t="s">
         <v>241</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -5974,9 +6020,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
       <c r="G6" s="13" t="s">
         <v>108</v>
       </c>
@@ -5991,9 +6037,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
       <c r="G7" s="13" t="s">
         <v>90</v>
       </c>
@@ -6008,9 +6054,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="33"/>
       <c r="G8" s="13" t="s">
         <v>92</v>
       </c>
@@ -6025,9 +6071,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
       <c r="G9" s="13" t="s">
         <v>93</v>
       </c>
@@ -6042,9 +6088,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
       <c r="G10" s="13" t="s">
         <v>83</v>
       </c>
@@ -6059,9 +6105,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
       <c r="G11" s="13" t="s">
         <v>120</v>
       </c>
@@ -6076,9 +6122,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33"/>
       <c r="G12" s="13" t="s">
         <v>97</v>
       </c>
@@ -6093,9 +6139,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
       <c r="G13" s="13" t="s">
         <v>121</v>
       </c>
@@ -6110,9 +6156,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
       <c r="G14" s="13" t="s">
         <v>133</v>
       </c>
@@ -6127,9 +6173,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="33"/>
       <c r="G15" s="13" t="s">
         <v>132</v>
       </c>
@@ -6144,9 +6190,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="33"/>
       <c r="G16" s="16" t="s">
         <v>131</v>
       </c>
@@ -6457,11 +6503,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -6476,11 +6522,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="22" t="s">
         <v>123</v>
       </c>
@@ -6518,13 +6564,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="31" t="s">
         <v>240</v>
       </c>
       <c r="G5" s="16" t="s">
@@ -6541,9 +6587,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
       <c r="G6" s="16" t="s">
         <v>112</v>
       </c>
@@ -6558,9 +6604,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
       <c r="G7" s="16" t="s">
         <v>143</v>
       </c>
@@ -6575,9 +6621,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="33"/>
       <c r="G8" s="16" t="s">
         <v>144</v>
       </c>
@@ -6592,9 +6638,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
       <c r="G9" s="16" t="s">
         <v>108</v>
       </c>
@@ -6609,9 +6655,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
       <c r="G10" s="16" t="s">
         <v>90</v>
       </c>
@@ -6626,9 +6672,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
       <c r="G11" s="16" t="s">
         <v>145</v>
       </c>
@@ -6643,9 +6689,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33"/>
       <c r="G12" s="16" t="s">
         <v>146</v>
       </c>
@@ -6660,9 +6706,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
       <c r="G13" s="16" t="s">
         <v>106</v>
       </c>
@@ -6677,9 +6723,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
       <c r="G14" s="16" t="s">
         <v>97</v>
       </c>
@@ -6694,9 +6740,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="33"/>
       <c r="G15" s="16" t="s">
         <v>113</v>
       </c>
@@ -6711,9 +6757,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="33"/>
       <c r="G16" s="16" t="s">
         <v>148</v>
       </c>
@@ -7124,11 +7170,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -7143,11 +7189,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
@@ -7185,13 +7231,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="31" t="s">
         <v>243</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -7208,9 +7254,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
       <c r="G6" s="26" t="s">
         <v>97</v>
       </c>
@@ -7225,9 +7271,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
       <c r="G7" s="26" t="s">
         <v>175</v>
       </c>
@@ -7242,9 +7288,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="33"/>
       <c r="G8" s="17" t="s">
         <v>176</v>
       </c>
@@ -7259,9 +7305,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
       <c r="G9" s="17" t="s">
         <v>177</v>
       </c>
@@ -7276,9 +7322,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
       <c r="G10" s="17" t="s">
         <v>178</v>
       </c>
@@ -7293,9 +7339,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
       <c r="G11" s="17" t="s">
         <v>182</v>
       </c>
@@ -7310,9 +7356,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33"/>
       <c r="G12" s="17" t="s">
         <v>179</v>
       </c>
@@ -7327,9 +7373,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
       <c r="G13" s="17" t="s">
         <v>180</v>
       </c>
@@ -7344,9 +7390,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
       <c r="G14" s="17" t="s">
         <v>181</v>
       </c>
@@ -7361,9 +7407,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="33"/>
       <c r="G15" s="17" t="s">
         <v>106</v>
       </c>
@@ -7378,9 +7424,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="33"/>
       <c r="G16" s="14" t="s">
         <v>95</v>
       </c>
@@ -7811,11 +7857,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -7830,11 +7876,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="6" t="s">
         <v>82</v>
       </c>
@@ -7871,14 +7917,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+    <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="31" t="s">
         <v>246</v>
       </c>
       <c r="G5" s="9" t="s">
@@ -7895,9 +7941,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
       <c r="G6" s="14" t="s">
         <v>204</v>
       </c>
@@ -7912,9 +7958,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
       <c r="G7" s="14" t="s">
         <v>106</v>
       </c>
@@ -7929,9 +7975,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="33"/>
       <c r="G8" s="14" t="s">
         <v>90</v>
       </c>
@@ -7946,9 +7992,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
       <c r="G9" s="14" t="s">
         <v>121</v>
       </c>
@@ -7963,9 +8009,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
       <c r="G10" s="16" t="s">
         <v>104</v>
       </c>
@@ -7980,9 +8026,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
       <c r="G11" s="16" t="s">
         <v>159</v>
       </c>
@@ -7997,9 +8043,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33"/>
       <c r="G12" s="16" t="s">
         <v>150</v>
       </c>
@@ -8014,9 +8060,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
       <c r="G13" s="16" t="s">
         <v>148</v>
       </c>
@@ -8031,9 +8077,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
       <c r="G14" s="16" t="s">
         <v>153</v>
       </c>
@@ -8048,9 +8094,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="33"/>
       <c r="G15" s="13" t="s">
         <v>108</v>
       </c>
@@ -8065,9 +8111,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="33"/>
       <c r="G16" s="13" t="s">
         <v>175</v>
       </c>
@@ -8383,6 +8429,7 @@
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8398,11 +8445,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
       <c r="G2" s="2" t="s">
         <v>80</v>
       </c>
@@ -8417,11 +8464,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
       <c r="G3" s="21" t="s">
         <v>97</v>
       </c>
@@ -8459,13 +8506,13 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="31" t="s">
         <v>240</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -8482,9 +8529,9 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
       <c r="G6" s="13" t="s">
         <v>142</v>
       </c>
@@ -8499,9 +8546,9 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
       <c r="G7" s="13" t="s">
         <v>175</v>
       </c>
@@ -8516,9 +8563,9 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="33"/>
       <c r="G8" s="13" t="s">
         <v>215</v>
       </c>
@@ -8533,9 +8580,9 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
       <c r="G9" s="13" t="s">
         <v>90</v>
       </c>
@@ -8550,9 +8597,9 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
       <c r="G10" s="13" t="s">
         <v>104</v>
       </c>
@@ -8567,9 +8614,9 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
       <c r="G11" s="13" t="s">
         <v>93</v>
       </c>
@@ -8584,9 +8631,9 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33"/>
       <c r="G12" s="9" t="s">
         <v>216</v>
       </c>
@@ -8601,9 +8648,9 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
       <c r="G13" s="26" t="s">
         <v>92</v>
       </c>
@@ -8618,9 +8665,9 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
       <c r="G14" s="26" t="s">
         <v>143</v>
       </c>
@@ -8635,9 +8682,9 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="33"/>
       <c r="G15" s="26" t="s">
         <v>101</v>
       </c>
@@ -8652,9 +8699,9 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="33"/>
       <c r="G16" s="26" t="s">
         <v>113</v>
       </c>
